--- a/giro_da_praça_ofertas - ARRASADORAS - SEG A QUA.xlsx
+++ b/giro_da_praça_ofertas - ARRASADORAS - SEG A QUA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workflow\automacao_giro_ofertas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BCEE3CD-81C7-4709-9287-1129C36B1067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19E3F44B-1B7B-4861-9253-76A84F4571AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -169,7 +169,7 @@
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE</t>
   </si>
   <si>
-    <t>LEITE LONGA VIDA TRIANGULO 1L INTEGRAL</t>
+    <t>LEITE LONGA VIDA PIRACANJUBA 1L INTEGRAL</t>
   </si>
   <si>
     <t>#02 MERCEARIA - LATICÍNIOS - LEITE EM PÓ</t>
@@ -287,7 +287,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -304,6 +304,12 @@
     <font>
       <sz val="7"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="7"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -327,6 +333,13 @@
       <family val="2"/>
     </font>
     <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -334,7 +347,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -345,6 +358,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF45A045"/>
+        <bgColor rgb="FF45A045"/>
       </patternFill>
     </fill>
   </fills>
@@ -375,7 +394,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -383,32 +402,38 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -715,26 +740,27 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F56"/>
-  <sheetFormatPr defaultRowHeight="21" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="42.75" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="36.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.42578125" style="9" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.85546875" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.5703125" style="11" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="43.85546875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="36.5703125" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.42578125" style="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.140625" style="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.5703125" style="14" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="42" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="4" t="s">
@@ -744,929 +770,929 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="6">
         <v>100038</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="7"/>
-      <c r="F2" s="8">
+      <c r="E2" s="8"/>
+      <c r="F2" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="12">
+      <c r="C3" s="6">
         <v>325990</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="8">
+      <c r="E3" s="8"/>
+      <c r="F3" s="9">
         <v>21.99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="6">
         <v>225003</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="7"/>
-      <c r="F4" s="8">
+      <c r="E4" s="8"/>
+      <c r="F4" s="9">
         <v>20.99</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12">
+      <c r="C5" s="6">
         <v>327443</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="7"/>
-      <c r="F5" s="8">
+      <c r="E5" s="8"/>
+      <c r="F5" s="9">
         <v>9.7899999999999991</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="6">
         <v>167128</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="F6" s="8">
+      <c r="E6" s="8"/>
+      <c r="F6" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="12">
+      <c r="C7" s="6">
         <v>345404</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="7"/>
-      <c r="F7" s="8">
+      <c r="E7" s="8"/>
+      <c r="F7" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="2" t="s">
+    <row r="9" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="10">
         <v>255232</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8">
-        <v>19.989999999999998</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="E9" s="11"/>
+      <c r="F9" s="12">
+        <v>18.989999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="10">
         <v>101137</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E10" s="7"/>
-      <c r="F10" s="8">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="11"/>
+      <c r="F10" s="12">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="6">
         <v>114037</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="7"/>
-      <c r="F11" s="8">
+      <c r="E11" s="8"/>
+      <c r="F11" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="6">
         <v>186826</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="7"/>
-      <c r="F12" s="8">
+      <c r="E12" s="8"/>
+      <c r="F12" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="6">
         <v>257157</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="8">
+      <c r="E13" s="8"/>
+      <c r="F13" s="9">
         <v>8.69</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="2" t="s">
+    <row r="14" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="10">
         <v>341362</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8">
-        <v>13.99</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E14" s="11"/>
+      <c r="F14" s="12">
+        <v>12.99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="6">
         <v>132657</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="7"/>
-      <c r="F15" s="8">
+      <c r="E15" s="8"/>
+      <c r="F15" s="9">
         <v>49.99</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="6">
         <v>337322</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="8">
+      <c r="E16" s="8"/>
+      <c r="F16" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="6">
         <v>273714</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="8">
+      <c r="E17" s="8"/>
+      <c r="F17" s="9">
         <v>7.89</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="6">
         <v>135408</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="7"/>
-      <c r="F18" s="8">
+      <c r="E18" s="8"/>
+      <c r="F18" s="9">
         <v>14.99</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="6">
         <v>101728</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="E19" s="7"/>
-      <c r="F19" s="8">
+      <c r="E19" s="8"/>
+      <c r="F19" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="6">
         <v>321107</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="8">
+      <c r="E20" s="8"/>
+      <c r="F20" s="9">
         <v>1.89</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="6">
         <v>100876</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="7"/>
-      <c r="F21" s="8">
+      <c r="E21" s="8"/>
+      <c r="F21" s="9">
         <v>18.989999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="6">
         <v>141367</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="E22" s="7"/>
-      <c r="F22" s="8">
+      <c r="E22" s="8"/>
+      <c r="F22" s="9">
         <v>3.69</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="6">
         <v>130920</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="8">
+      <c r="E23" s="8"/>
+      <c r="F23" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="6">
         <v>100706</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="8">
+      <c r="E24" s="8"/>
+      <c r="F24" s="9">
         <v>6.99</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="6">
         <v>221089</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="7"/>
-      <c r="F25" s="8">
+      <c r="E25" s="8"/>
+      <c r="F25" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="6">
         <v>100027</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="E26" s="7"/>
-      <c r="F26" s="8">
+      <c r="E26" s="8"/>
+      <c r="F26" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B27" s="2" t="s">
+    <row r="27" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="10">
         <v>100120</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E27" s="7"/>
-      <c r="F27" s="8">
-        <v>2.69</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E27" s="11"/>
+      <c r="F27" s="12">
+        <v>2.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="6">
         <v>149121</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="E28" s="7"/>
-      <c r="F28" s="8">
+      <c r="E28" s="8"/>
+      <c r="F28" s="9">
         <v>3.99</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="6">
         <v>128920</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="E29" s="7"/>
-      <c r="F29" s="8">
+      <c r="E29" s="8"/>
+      <c r="F29" s="9">
         <v>8.99</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="6">
         <v>193295</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="E30" s="7"/>
-      <c r="F30" s="8">
+      <c r="E30" s="8"/>
+      <c r="F30" s="9">
         <v>3.49</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="6">
         <v>220451</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="E31" s="7"/>
-      <c r="F31" s="8">
+      <c r="E31" s="8"/>
+      <c r="F31" s="9">
         <v>6.89</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B32" s="2" t="s">
+    <row r="32" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B32" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C32" s="12">
-        <v>111530</v>
-      </c>
-      <c r="D32" s="6" t="s">
+      <c r="C32" s="10">
+        <v>101113</v>
+      </c>
+      <c r="D32" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="7"/>
-      <c r="F32" s="8">
-        <v>5.19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E32" s="11"/>
+      <c r="F32" s="12">
+        <v>8.59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="6">
         <v>106922</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="8">
+      <c r="E33" s="8"/>
+      <c r="F33" s="9">
         <v>38.99</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="6">
         <v>307145</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="8">
+      <c r="E34" s="8"/>
+      <c r="F34" s="9">
         <v>20.89</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="6">
         <v>290255</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="E35" s="7"/>
-      <c r="F35" s="8">
+      <c r="E35" s="8"/>
+      <c r="F35" s="9">
         <v>3.89</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="6">
         <v>106791</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E36" s="7"/>
-      <c r="F36" s="8">
+      <c r="E36" s="8"/>
+      <c r="F36" s="9">
         <v>3.19</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="6">
         <v>104406</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="E38" s="7"/>
-      <c r="F38" s="8">
+      <c r="E38" s="8"/>
+      <c r="F38" s="9">
         <v>10.99</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="6">
         <v>104404</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="E39" s="7"/>
-      <c r="F39" s="8">
+      <c r="E39" s="8"/>
+      <c r="F39" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="6">
         <v>104410</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E40" s="7"/>
-      <c r="F40" s="8">
+      <c r="E40" s="8"/>
+      <c r="F40" s="9">
         <v>9.99</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="6">
         <v>102237</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="E41" s="7"/>
-      <c r="F41" s="8">
+      <c r="E41" s="8"/>
+      <c r="F41" s="9">
         <v>24.99</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="6">
         <v>102149</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E42" s="7"/>
-      <c r="F42" s="8">
+      <c r="E42" s="8"/>
+      <c r="F42" s="9">
         <v>5.99</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="6">
         <v>247799</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E43" s="7"/>
-      <c r="F43" s="8">
+      <c r="E43" s="8"/>
+      <c r="F43" s="9">
         <v>6.49</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="2" t="s">
+    <row r="44" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="10">
         <v>168712</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="7"/>
-      <c r="F44" s="8">
-        <f>15*3.39</f>
-        <v>50.85</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B45" s="2" t="s">
+      <c r="E44" s="11"/>
+      <c r="F44" s="12">
+        <f>15*3.19</f>
+        <v>47.85</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="10">
         <v>324556</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="E45" s="7"/>
-      <c r="F45" s="8">
+      <c r="E45" s="11"/>
+      <c r="F45" s="12">
         <f>15*2.99</f>
         <v>44.85</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="6">
         <v>102085</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="E46" s="7"/>
-      <c r="F46" s="8">
+      <c r="E46" s="8"/>
+      <c r="F46" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B47" s="2" t="s">
+    <row r="47" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="10">
         <v>295198</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E47" s="7"/>
-      <c r="F47" s="8">
-        <v>11.69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E47" s="11"/>
+      <c r="F47" s="12">
+        <v>10.99</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="6">
         <v>207640</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="E49" s="7"/>
-      <c r="F49" s="8">
+      <c r="E49" s="8"/>
+      <c r="F49" s="9">
         <v>7.99</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="6">
         <v>330053</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="E50" s="7"/>
-      <c r="F50" s="8">
+      <c r="E50" s="8"/>
+      <c r="F50" s="9">
         <v>9.89</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="6">
         <v>148554</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="E51" s="7"/>
-      <c r="F51" s="8">
+      <c r="E51" s="8"/>
+      <c r="F51" s="9">
         <v>12.99</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="6">
         <v>100391</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="E52" s="7"/>
-      <c r="F52" s="8">
+      <c r="E52" s="8"/>
+      <c r="F52" s="9">
         <v>2.99</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="6">
         <v>100511</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="E53" s="7"/>
-      <c r="F53" s="8">
+      <c r="E53" s="8"/>
+      <c r="F53" s="9">
         <v>4.99</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="6">
         <v>261980</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="E54" s="7"/>
-      <c r="F54" s="8">
+      <c r="E54" s="8"/>
+      <c r="F54" s="9">
         <v>17.989999999999998</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="6">
         <v>346964</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="8">
+      <c r="E56" s="8"/>
+      <c r="F56" s="9">
         <v>13.99</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.74803149606299213" right="0.74803149606299213" top="0.98425196850393704" bottom="0.98425196850393704" header="0.51181102362204722" footer="0.51181102362204722"/>
-  <pageSetup paperSize="9" scale="71" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;LGIRO DA PRAÇA - ARRASADORAS - SEGUNDA A QUARTA&amp;C&amp;P - &amp;N</oddHeader>
   </headerFooter>
